--- a/amitdusane-site-complete/static/templates/adobe-analytics-implementation-project-plan-template.xlsx
+++ b/amitdusane-site-complete/static/templates/adobe-analytics-implementation-project-plan-template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/25ed449a1af7f163/Documents/Claude Code/Adobe Analytics/amitdusane-site-complete/static/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{547C08C2-52E0-44A2-BB4E-D643D87F77A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EADF8698-54CE-4C65-BD7D-AE8BA70CF1BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{3F876DD1-BA56-45BD-A541-474709755655}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{8AFD99F2-9BE1-49A1-BB0A-7DFC5BA5C243}"/>
   </bookViews>
   <sheets>
     <sheet name="Plan" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
     <author>Amit Dusane</author>
   </authors>
   <commentList>
-    <comment ref="B3" authorId="0" shapeId="0" xr:uid="{A11BE401-4499-4A4A-9FC6-E47981EB4F18}">
+    <comment ref="B3" authorId="0" shapeId="0" xr:uid="{D4F61578-38E0-4D1F-91ED-3A8282803974}">
       <text>
         <r>
           <rPr>
@@ -57,7 +57,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C3" authorId="0" shapeId="0" xr:uid="{5BEAE12A-D49E-41AA-A52D-B43C802F5262}">
+    <comment ref="C3" authorId="0" shapeId="0" xr:uid="{62B3CE71-A424-4444-95C6-FAE5D0FEC857}">
       <text>
         <r>
           <rPr>
@@ -71,7 +71,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D3" authorId="0" shapeId="0" xr:uid="{D9A7BD23-B9A2-4F39-BA74-3DABFA02D5F4}">
+    <comment ref="D3" authorId="0" shapeId="0" xr:uid="{D76E6F83-725C-43AD-B61E-6966E8F4DBFC}">
       <text>
         <r>
           <rPr>
@@ -85,7 +85,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E3" authorId="0" shapeId="0" xr:uid="{5C4BFC4D-2852-4E0E-9583-B10B6B89B0DA}">
+    <comment ref="E3" authorId="0" shapeId="0" xr:uid="{63FA6EF0-7F40-4EF7-B058-20296274F412}">
       <text>
         <r>
           <rPr>
@@ -99,7 +99,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F3" authorId="0" shapeId="0" xr:uid="{672B4E98-2385-4DC3-A650-0D8E5E231E64}">
+    <comment ref="F3" authorId="0" shapeId="0" xr:uid="{90EA8E90-02A5-470F-A8CC-A3A6145085DF}">
       <text>
         <r>
           <rPr>
@@ -113,7 +113,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G3" authorId="0" shapeId="0" xr:uid="{718541B1-E9BB-4633-B2CC-E00731BD8014}">
+    <comment ref="G3" authorId="0" shapeId="0" xr:uid="{D4CDC5FF-446C-46AF-9BFC-1EDE6851B835}">
       <text>
         <r>
           <rPr>
@@ -127,7 +127,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H3" authorId="0" shapeId="0" xr:uid="{61925597-C961-4D7F-859E-140EED2BF6B5}">
+    <comment ref="H3" authorId="0" shapeId="0" xr:uid="{21E4BBCB-FC48-4D4C-91D1-BE85A97941B2}">
       <text>
         <r>
           <rPr>
@@ -146,7 +146,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="107">
   <si>
     <t>Kestrel and Co. Website - Analytics Implementation Plan - Phase 1</t>
   </si>
@@ -175,13 +175,10 @@
     <t>Status</t>
   </si>
   <si>
-    <t>1</t>
-  </si>
-  <si>
     <t>Discovery workshop with business, ecommerce and marketing</t>
   </si>
   <si>
-    <t>Us, Kestrel</t>
+    <t>Analytics team, Kestrel business team</t>
   </si>
   <si>
     <t>Requirement notes</t>
@@ -193,19 +190,13 @@
     <t>03 Mar</t>
   </si>
   <si>
-    <t>12</t>
-  </si>
-  <si>
     <t>Done</t>
   </si>
   <si>
-    <t>2</t>
-  </si>
-  <si>
     <t>Draft the business requirements</t>
   </si>
   <si>
-    <t>Us</t>
+    <t>Analytics team</t>
   </si>
   <si>
     <t>BRD version 1.0 draft</t>
@@ -217,12 +208,6 @@
     <t>09 Mar</t>
   </si>
   <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
     <t>Review and prioritise, agree phases</t>
   </si>
   <si>
@@ -232,16 +217,10 @@
     <t>13 Mar</t>
   </si>
   <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
     <t>Sign off the BRD</t>
   </si>
   <si>
-    <t>Kestrel</t>
+    <t>Kestrel business team</t>
   </si>
   <si>
     <t>BRD version 1.0 signed</t>
@@ -250,9 +229,6 @@
     <t>16 Mar</t>
   </si>
   <si>
-    <t>5</t>
-  </si>
-  <si>
     <t>Design the solution</t>
   </si>
   <si>
@@ -265,12 +241,6 @@
     <t>20 Mar</t>
   </si>
   <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
     <t>SDR review and revisions</t>
   </si>
   <si>
@@ -283,9 +253,6 @@
     <t>09 Apr</t>
   </si>
   <si>
-    <t>7</t>
-  </si>
-  <si>
     <t>Sign off the SDR</t>
   </si>
   <si>
@@ -307,63 +274,48 @@
     <t>16 Apr</t>
   </si>
   <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
     <t>Walkthrough with the development team</t>
   </si>
   <si>
+    <t>Analytics team, Kestrel web dev</t>
+  </si>
+  <si>
     <t>11 May</t>
   </si>
   <si>
-    <t>10</t>
-  </si>
-  <si>
     <t>Data layer development</t>
   </si>
   <si>
+    <t>Kestrel web dev</t>
+  </si>
+  <si>
     <t>20 Apr</t>
   </si>
   <si>
     <t>15 May</t>
   </si>
   <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
     <t>Tag manager build, development environment</t>
   </si>
   <si>
-    <t>40</t>
-  </si>
-  <si>
     <t>Report suite configuration</t>
   </si>
   <si>
     <t>24 Apr</t>
   </si>
   <si>
-    <t>13</t>
-  </si>
-  <si>
     <t>Validation cycle 1, staging</t>
   </si>
   <si>
+    <t>Analytics team, Kestrel QA</t>
+  </si>
+  <si>
     <t>Validation Report, cycle 1</t>
   </si>
   <si>
     <t>22 May</t>
   </si>
   <si>
-    <t>14</t>
-  </si>
-  <si>
     <t>Fixes from cycle 1</t>
   </si>
   <si>
@@ -373,9 +325,6 @@
     <t>28 May</t>
   </si>
   <si>
-    <t>15</t>
-  </si>
-  <si>
     <t>Validation cycle 2, staging</t>
   </si>
   <si>
@@ -394,9 +343,6 @@
     <t>03 Jun</t>
   </si>
   <si>
-    <t>17</t>
-  </si>
-  <si>
     <t>Validation cycle 3, staging</t>
   </si>
   <si>
@@ -406,9 +352,6 @@
     <t>04 Jun</t>
   </si>
   <si>
-    <t>18</t>
-  </si>
-  <si>
     <t>Publish to production</t>
   </si>
   <si>
@@ -418,9 +361,6 @@
     <t>Not started</t>
   </si>
   <si>
-    <t>19</t>
-  </si>
-  <si>
     <t>Production check, one cycle</t>
   </si>
   <si>
@@ -445,9 +385,6 @@
     <t>18 Jun</t>
   </si>
   <si>
-    <t>21</t>
-  </si>
-  <si>
     <t>Phase 1 patch: sign out, form tracking, Named Day view</t>
   </si>
   <si>
@@ -463,9 +400,6 @@
     <t>Total hours</t>
   </si>
   <si>
-    <t>246</t>
-  </si>
-  <si>
     <t>Assumptions and dependencies - the things that will move the date if they are not true</t>
   </si>
   <si>
@@ -481,7 +415,7 @@
     <t>A2</t>
   </si>
   <si>
-    <t>Data layer development is done by Kestrel and Co. Twenty working days are assigned. This is the single activity most likely to move the go live date, because nothing else can be tested until it exists.</t>
+    <t>Data layer development is done by Kestrel web dev. Twenty working days are assigned. This is the single activity most likely to move the go live date, because nothing else can be tested until it exists.</t>
   </si>
   <si>
     <t>A3</t>
@@ -493,7 +427,10 @@
     <t>A4</t>
   </si>
   <si>
-    <t>Kestrel and Co. provide a tester for each cycle. Validation with one person takes twice as long and finds less.</t>
+    <t>Kestrel QA provide a tester for each cycle. Validation with one person takes twice as long and finds less.</t>
+  </si>
+  <si>
+    <t>Kestrel QA</t>
   </si>
   <si>
     <t>A5</t>
@@ -609,12 +546,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -932,7 +876,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61984676-DBE9-45A1-AF6E-D89CBD07F3DA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{915FDEB5-4D21-43E4-96D7-1899BC6BD6AF}">
   <sheetPr>
     <tabColor rgb="FF0070C0"/>
   </sheetPr>
@@ -943,7 +887,8 @@
     <col min="2" max="2" width="52.59765625" style="2" customWidth="1"/>
     <col min="3" max="3" width="20.59765625" style="2" customWidth="1"/>
     <col min="4" max="4" width="38.59765625" style="2" customWidth="1"/>
-    <col min="5" max="8" width="14.59765625" style="2" customWidth="1"/>
+    <col min="5" max="6" width="14.59765625" style="3" customWidth="1"/>
+    <col min="7" max="8" width="14.59765625" style="2" customWidth="1"/>
     <col min="9" max="16384" width="9.06640625" style="2"/>
   </cols>
   <sheetData>
@@ -953,582 +898,582 @@
       </c>
     </row>
     <row r="3" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A4" s="4" t="s">
+    <row r="4" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A4" s="6">
+        <v>1</v>
+      </c>
+      <c r="B4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="C4" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="D4" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="E4" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="F4" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="F4" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="6">
+        <v>12</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A5" s="6">
+        <v>2</v>
+      </c>
+      <c r="B5" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="C5" s="6" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A5" s="4" t="s">
+      <c r="D5" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="E5" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="F5" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="G5" s="6">
+        <v>16</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A6" s="6">
+        <v>3</v>
+      </c>
+      <c r="B6" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="C6" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="6"/>
+      <c r="E6" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F6" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G6" s="6">
+        <v>8</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A7" s="6">
+        <v>4</v>
+      </c>
+      <c r="B7" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="C7" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G7" s="6">
+        <v>2</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A8" s="6">
+        <v>5</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="6" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A6" s="4" t="s">
+      <c r="D8" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="G8" s="6">
         <v>24</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" s="4" t="s">
+      <c r="H8" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A9" s="6">
+        <v>6</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="G9" s="6">
+        <v>12</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A10" s="6">
+        <v>7</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="G10" s="6">
+        <v>2</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A11" s="6">
+        <v>8</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="G11" s="6">
+        <v>20</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A12" s="6">
+        <v>9</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D12" s="6"/>
+      <c r="E12" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="G12" s="6">
+        <v>4</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A13" s="6">
+        <v>10</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="D13" s="6"/>
+      <c r="E13" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="G13" s="6">
+        <v>0</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A14" s="6">
         <v>11</v>
       </c>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H6" s="4" t="s">
+      <c r="B14" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C14" s="6" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A7" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="G7" s="4" t="s">
+      <c r="D14" s="6"/>
+      <c r="E14" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="G14" s="6">
+        <v>40</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A15" s="6">
+        <v>12</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D15" s="6"/>
+      <c r="E15" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="G15" s="6">
+        <v>8</v>
+      </c>
+      <c r="H15" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A16" s="6">
+        <v>13</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="G16" s="6">
+        <v>12</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A17" s="6">
+        <v>14</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D17" s="6"/>
+      <c r="E17" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="G17" s="6">
+        <v>16</v>
+      </c>
+      <c r="H17" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A18" s="6">
+        <v>15</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="G18" s="6">
+        <v>10</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A19" s="6">
+        <v>16</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D19" s="6"/>
+      <c r="E19" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="G19" s="6">
+        <v>12</v>
+      </c>
+      <c r="H19" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A20" s="6">
         <v>17</v>
       </c>
-      <c r="H7" s="4" t="s">
+      <c r="B20" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="G20" s="6">
+        <v>8</v>
+      </c>
+      <c r="H20" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A21" s="6">
+        <v>18</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C21" s="6" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A8" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C8" s="4" t="s">
+      <c r="D21" s="6"/>
+      <c r="E21" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="G21" s="6">
+        <v>4</v>
+      </c>
+      <c r="H21" s="6" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A22" s="6">
         <v>19</v>
       </c>
-      <c r="D8" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="H8" s="4" t="s">
+      <c r="B22" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="G22" s="6">
+        <v>8</v>
+      </c>
+      <c r="H22" s="6" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A23" s="6">
+        <v>20</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C23" s="6" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A9" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="E9" s="4" t="s">
+      <c r="D23" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="G23" s="6">
+        <v>16</v>
+      </c>
+      <c r="H23" s="6" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A24" s="6">
+        <v>21</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C24" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="F9" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A10" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A11" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A12" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A13" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="H13" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A14" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="H14" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A15" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H15" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A16" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H16" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A17" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="H17" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A18" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="G18" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="H18" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A19" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4" t="s">
+      <c r="D24" s="6"/>
+      <c r="E24" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="F19" s="4" t="s">
+      <c r="F24" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="G19" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H19" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A20" s="4" t="s">
+      <c r="G24" s="6">
+        <v>12</v>
+      </c>
+      <c r="H24" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="B20" s="4" t="s">
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A25" s="6"/>
+      <c r="B25" s="6"/>
+      <c r="C25" s="6"/>
+      <c r="D25" s="6"/>
+      <c r="E25" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="C20" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="G20" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H20" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A21" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="G21" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="H21" s="4" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A22" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="E22" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="F22" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="G22" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H22" s="4" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A23" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="E23" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="F23" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="G23" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="H23" s="4" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A24" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D24" s="4"/>
-      <c r="E24" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="F24" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="G24" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H24" s="4" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A25" s="4"/>
-      <c r="B25" s="4"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="4"/>
-      <c r="E25" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="F25" s="4"/>
-      <c r="G25" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="H25" s="4"/>
+      <c r="F25" s="7"/>
+      <c r="G25" s="6">
+        <v>246</v>
+      </c>
+      <c r="H25" s="6"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:H25" xr:uid="{61984676-DBE9-45A1-AF6E-D89CBD07F3DA}"/>
+  <autoFilter ref="A3:H25" xr:uid="{915FDEB5-4D21-43E4-96D7-1899BC6BD6AF}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1081027C-B854-422B-99FE-C1054D8651DB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1B944B8-6CEC-4ED3-924C-AAFC78BB87E2}">
   <sheetPr>
     <tabColor rgb="FFD04646"/>
   </sheetPr>
@@ -1543,128 +1488,128 @@
   <sheetData>
     <row r="1" spans="1:3" ht="16.899999999999999" x14ac:dyDescent="0.5">
       <c r="A1" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A3" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A4" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A5" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A6" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A7" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A8" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A9" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A10" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A11" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A12" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A13" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="B13" s="6" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A4" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A5" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A6" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A7" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A8" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A9" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A10" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A11" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A12" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A13" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>31</v>
+      <c r="C13" s="6" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>

--- a/amitdusane-site-complete/static/templates/adobe-analytics-implementation-project-plan-template.xlsx
+++ b/amitdusane-site-complete/static/templates/adobe-analytics-implementation-project-plan-template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/25ed449a1af7f163/Documents/Claude Code/Adobe Analytics/amitdusane-site-complete/static/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EADF8698-54CE-4C65-BD7D-AE8BA70CF1BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{807991DB-AC39-4439-AF21-157A6CA585C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{8AFD99F2-9BE1-49A1-BB0A-7DFC5BA5C243}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{98B1A74D-5795-42C4-A114-968611C6F090}"/>
   </bookViews>
   <sheets>
     <sheet name="Plan" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
     <author>Amit Dusane</author>
   </authors>
   <commentList>
-    <comment ref="B3" authorId="0" shapeId="0" xr:uid="{D4F61578-38E0-4D1F-91ED-3A8282803974}">
+    <comment ref="B3" authorId="0" shapeId="0" xr:uid="{FB6F3AE8-6AE9-4C79-BCE9-BDF03FDCC5E3}">
       <text>
         <r>
           <rPr>
@@ -57,7 +57,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C3" authorId="0" shapeId="0" xr:uid="{62B3CE71-A424-4444-95C6-FAE5D0FEC857}">
+    <comment ref="C3" authorId="0" shapeId="0" xr:uid="{8CC5C55A-B6D0-4231-8EA1-1328635D91BF}">
       <text>
         <r>
           <rPr>
@@ -71,7 +71,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D3" authorId="0" shapeId="0" xr:uid="{D76E6F83-725C-43AD-B61E-6966E8F4DBFC}">
+    <comment ref="D3" authorId="0" shapeId="0" xr:uid="{2B7CABAC-BBC8-43D0-A486-18FF2549ABA3}">
       <text>
         <r>
           <rPr>
@@ -85,7 +85,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E3" authorId="0" shapeId="0" xr:uid="{63FA6EF0-7F40-4EF7-B058-20296274F412}">
+    <comment ref="E3" authorId="0" shapeId="0" xr:uid="{58C6D5FF-F217-4526-A8DD-110B181C93FD}">
       <text>
         <r>
           <rPr>
@@ -99,7 +99,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F3" authorId="0" shapeId="0" xr:uid="{90EA8E90-02A5-470F-A8CC-A3A6145085DF}">
+    <comment ref="F3" authorId="0" shapeId="0" xr:uid="{F236FE0D-537B-4380-9BBB-985682D403AE}">
       <text>
         <r>
           <rPr>
@@ -113,7 +113,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G3" authorId="0" shapeId="0" xr:uid="{D4CDC5FF-446C-46AF-9BFC-1EDE6851B835}">
+    <comment ref="G3" authorId="0" shapeId="0" xr:uid="{6C7C47C8-8EAB-4AD2-A093-C6E3F584CF5E}">
       <text>
         <r>
           <rPr>
@@ -127,7 +127,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H3" authorId="0" shapeId="0" xr:uid="{21E4BBCB-FC48-4D4C-91D1-BE85A97941B2}">
+    <comment ref="H3" authorId="0" shapeId="0" xr:uid="{12B20C97-CEDA-4991-98A0-123B2C803A66}">
       <text>
         <r>
           <rPr>
@@ -146,7 +146,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="108">
   <si>
     <t>Kestrel and Co. Website - Analytics Implementation Plan - Phase 1</t>
   </si>
@@ -398,6 +398,9 @@
   </si>
   <si>
     <t>Total hours</t>
+  </si>
+  <si>
+    <t>Template from amitdusane.com  |  Amit G Dusane</t>
   </si>
   <si>
     <t>Assumptions and dependencies - the things that will move the date if they are not true</t>
@@ -473,7 +476,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -503,6 +506,14 @@
       <color indexed="81"/>
       <name val="Tahoma"/>
       <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FF808080"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -546,7 +557,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -563,6 +574,7 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -876,11 +888,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{915FDEB5-4D21-43E4-96D7-1899BC6BD6AF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D98387C8-4838-4179-95FA-CA805E5EEE5F}">
   <sheetPr>
     <tabColor rgb="FF0070C0"/>
   </sheetPr>
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="6.59765625" style="2" customWidth="1"/>
@@ -1465,19 +1477,27 @@
       </c>
       <c r="H25" s="6"/>
     </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A27" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:H25" xr:uid="{915FDEB5-4D21-43E4-96D7-1899BC6BD6AF}"/>
+  <autoFilter ref="A3:H25" xr:uid="{D98387C8-4838-4179-95FA-CA805E5EEE5F}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddFooter>&amp;L&amp;"Calibri"&amp;8&amp;K808080Template from amitdusane.com   |   Amit G Dusane&amp;R&amp;"Calibri"&amp;8&amp;K808080Page &amp;P of &amp;N</oddFooter>
+  </headerFooter>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1B944B8-6CEC-4ED3-924C-AAFC78BB87E2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2F76CC9-CCC6-4BDF-B9DD-86236E6CD7FD}">
   <sheetPr>
     <tabColor rgb="FFD04646"/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="10.59765625" style="2" customWidth="1"/>
@@ -1488,7 +1508,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="16.899999999999999" x14ac:dyDescent="0.5">
       <c r="A1" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.45">
@@ -1496,7 +1516,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>3</v>
@@ -1504,10 +1524,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>16</v>
@@ -1515,10 +1535,10 @@
     </row>
     <row r="5" spans="1:3" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A5" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>46</v>
@@ -1526,10 +1546,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A6" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>53</v>
@@ -1537,21 +1557,21 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A7" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A8" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>46</v>
@@ -1559,21 +1579,21 @@
     </row>
     <row r="9" spans="1:3" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A9" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A10" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>16</v>
@@ -1581,10 +1601,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A11" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>16</v>
@@ -1592,10 +1612,10 @@
     </row>
     <row r="12" spans="1:3" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A12" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>46</v>
@@ -1603,16 +1623,24 @@
     </row>
     <row r="13" spans="1:3" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A13" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>46</v>
       </c>
     </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A15" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddFooter>&amp;L&amp;"Calibri"&amp;8&amp;K808080Template from amitdusane.com   |   Amit G Dusane&amp;R&amp;"Calibri"&amp;8&amp;K808080Page &amp;P of &amp;N</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>